--- a/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:13</t>
+          <t>2026-10-06 01:24:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:14</t>
+          <t>2026-10-06 01:24:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:15</t>
+          <t>2026-10-06 01:24:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:17</t>
+          <t>2026-10-06 01:24:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:17</t>
+          <t>2026-10-06 01:24:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:17</t>
+          <t>2026-10-06 01:24:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:17</t>
+          <t>2026-10-06 01:24:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:17</t>
+          <t>2026-10-06 01:24:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.84%680,000</t>
+          <t>16.01%920,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.84%</t>
+          <t>16.01%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>680000</v>
+        <v>920000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.34%145.5</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>145.5</v>
+        <v>2050</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.12%3,734,000</t>
+          <t>4.57%326,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3734000</v>
+        <v>326000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.47%105.5</t>
+          <t>-2.19%380</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>105.5</v>
+        <v>380</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.10%5,127,000</t>
+          <t>4.15%1,581,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5127000</v>
+        <v>1581000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.02%388.5</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>388.5</v>
+        <v>744</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.99%1,414,000</t>
+          <t>3.68%734,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1414000</v>
+        <v>734000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+5.21%1715</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>742</v>
+        <v>1715</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.80%706,000</t>
+          <t>3.32%301,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>706000</v>
+        <v>301000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.35%740</t>
+          <t>-0.27%738</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.80%517,000</t>
+          <t>2.99%598,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>517000</v>
+        <v>598000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5165</v>
+        <v>625</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.50%67,000</t>
+          <t>2.94%694,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>67000</v>
+        <v>694000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>-0.95%104.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5700</v>
+        <v>104.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.43%62,000</t>
+          <t>2.80%3,926,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>62000</v>
+        <v>3926000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>626</v>
+        <v>7080</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.33%492,000</t>
+          <t>2.73%56,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>492000</v>
+        <v>56000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>152.5</v>
+        <v>3685</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.01%1,648,000</t>
+          <t>2.40%99,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1648000</v>
+        <v>99000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.76%1630</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.76%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1630</v>
+        <v>1310</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.99%177,000</t>
+          <t>2.40%268,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>177000</v>
+        <v>268000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>-0.95%1045</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3585</v>
+        <v>1045</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.84%71,000</t>
+          <t>2.40%336,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>71000</v>
+        <v>336000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.5%1055</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1055</v>
+        <v>5995</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.82%241,000</t>
+          <t>2.39%62,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>241000</v>
+        <v>62000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2150</v>
+        <v>4920</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.80%114,036</t>
+          <t>2.34%67,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>114036</v>
+        <v>67000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:50</t>
+          <t>2026-10-06 19:16:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7205</v>
+        <v>6855</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.75%34,000</t>
+          <t>2.27%50,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>34000</v>
+        <v>50000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.2%254</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>254</v>
+        <v>147.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.73%910,000</t>
+          <t>2.25%2,186,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>910000</v>
+        <v>2186000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>0%145.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2005</v>
+        <v>145.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.71%120,000</t>
+          <t>1.86%1,888,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>120000</v>
+        <v>1888000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.84%1180</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1180</v>
+        <v>2290</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.68%187,000</t>
+          <t>1.66%114,036</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>187000</v>
+        <v>114036</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.92%1705</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+4.92%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1705</v>
+        <v>2050</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.66%135,000</t>
+          <t>1.63%120,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>135000</v>
+        <v>120000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+0.79%256</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6730</v>
+        <v>256</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.62%34,000</t>
+          <t>1.56%910,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>34000</v>
+        <v>910000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%155</t>
+          <t>-3.23%1650</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>155</v>
+        <v>1650</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.52%1,302,000</t>
+          <t>1.56%135,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1302000</v>
+        <v>135000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>+2.12%1205</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1325</v>
+        <v>1205</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.51%153,000</t>
+          <t>1.49%187,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>153000</v>
+        <v>187000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.29%234.5</t>
+          <t>-3.74%592</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>234.5</v>
+        <v>592</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.43%787,000</t>
+          <t>1.48%357,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>787000</v>
+        <v>357000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,34 +1907,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>-2.28%1070</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2485</v>
+        <v>1070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.42%74,000</t>
+          <t>1.40%189,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>74000</v>
+        <v>189000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>0%155</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1495</v>
+        <v>155</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.41%128,000</t>
+          <t>1.36%1,302,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>128000</v>
+        <v>1302000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.23%20.1</t>
+          <t>-4.35%1980</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>20.1</v>
+        <v>1980</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.35%8,783,000</t>
+          <t>1.36%97,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>8783000</v>
+        <v>97000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>530</v>
+        <v>1505</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.23%310,000</t>
+          <t>1.29%128,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>310000</v>
+        <v>128000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.15%1190</t>
+          <t>+0.85%236.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1190</v>
+        <v>236.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.21%138,000</t>
+          <t>1.25%787,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>138000</v>
+        <v>787000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3000</v>
+        <v>2325</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.19%54,000</t>
+          <t>1.24%74,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>54000</v>
+        <v>74000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:52</t>
+          <t>2026-10-06 19:16:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>0%20.1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2075</v>
+        <v>20.1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.19%80,000</t>
+          <t>1.19%8,783,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>80000</v>
+        <v>8783000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1504東元</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1%69</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>69</v>
+        <v>13100</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.15%2,177,000</t>
+          <t>1.17%13,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2177000</v>
+        <v>13000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1605華新</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.9%38.4</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>38.4</v>
+        <v>525</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.06%3,636,000</t>
+          <t>1.11%310,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3636000</v>
+        <v>310000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+4.06%615</t>
+          <t>-1.26%1175</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>615</v>
+        <v>1175</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.97%217,000</t>
+          <t>1.11%138,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>217000</v>
+        <v>138000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+4.29%1095</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1095</v>
+        <v>2920</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.94%118,000</t>
+          <t>1.09%54,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>118000</v>
+        <v>54000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1101台泥</t>
+          <t>1504東元</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.38%25</t>
+          <t>+3.04%71.1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>25</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.93%4,878,000</t>
+          <t>1.02%2,177,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>4878000</v>
+        <v>2177000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%72.7</t>
+          <t>+1.55%5905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>72.7</v>
+        <v>5905</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.91%1,657,000</t>
+          <t>0.98%25,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1657000</v>
+        <v>25000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>1605華新</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+3.67%3950</t>
+          <t>+0.91%38.75</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3950</v>
+        <v>38.75</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.83%29,000</t>
+          <t>0.94%3,636,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>29000</v>
+        <v>3636000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>1101台泥</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.29%68.5</t>
+          <t>+0.8%25.2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>68.5</v>
+        <v>25.2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.82%1,589,000</t>
+          <t>0.82%4,878,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1589000</v>
+        <v>4878000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+9.81%2070</t>
+          <t>+1.38%73.7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+9.81%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2070</v>
+        <v>73.7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.77%54,000</t>
+          <t>0.81%1,657,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>54000</v>
+        <v>1657000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.21%5815</t>
+          <t>+5.82%4180</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+5.82%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5815</v>
+        <v>4180</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.76%18,000</t>
+          <t>0.77%29,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>18000</v>
+        <v>29000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.31%47.9</t>
+          <t>+0.15%68.6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>47.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.76%2,097,000</t>
+          <t>0.74%1,589,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2097000</v>
+        <v>1589000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.72%841</t>
+          <t>-0.42%47.7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>841</v>
+        <v>47.7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.64%102,000</t>
+          <t>0.68%2,097,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>102000</v>
+        <v>2097000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>+3.02%1535</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1595</v>
+        <v>1535</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.63%55,000</t>
+          <t>0.60%60,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+9.96%1490</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1490</v>
+        <v>1600</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.61%60,000</t>
+          <t>0.59%55,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:53</t>
+          <t>2026-10-06 19:16:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.12%181</t>
+          <t>+0.12%842</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>181</v>
+        <v>842</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.33%243,000</t>
+          <t>0.58%102,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>243000</v>
+        <v>102000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:54</t>
+          <t>2026-10-06 19:17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.14%216</t>
+          <t>-1.93%177.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>216</v>
+        <v>177.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.24%141,000</t>
+          <t>0.30%243,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>141000</v>
+        <v>243000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:54</t>
+          <t>2026-10-06 19:17:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3324雙鴻</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.99%1550</t>
+          <t>+0.23%216.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.99%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1550</v>
+        <v>216.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.20%18,000</t>
+          <t>0.21%141,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>18000</v>
+        <v>141000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:54</t>
+          <t>2026-10-06 19:17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>3324雙鴻</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1%152</t>
+          <t>-1.29%1530</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>152</v>
+        <v>1530</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.16%139,000</t>
+          <t>0.19%18,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>139000</v>
+        <v>18000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:54</t>
+          <t>2026-10-06 19:17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>+1.64%154.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13355</v>
+        <v>154.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.09%1,000</t>
+          <t>0.14%139,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>139000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:54</t>
+          <t>2026-10-06 19:17:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+9.95%1215</t>
+          <t>+3.7%1260</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1215</v>
+        <v>1260</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:56</t>
+          <t>2026-10-06 23:19:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:57</t>
+          <t>2026-10-06 23:19:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:59</t>
+          <t>2026-10-06 23:19:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:00</t>
+          <t>2026-10-06 23:19:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:00</t>
+          <t>2026-10-06 23:19:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:00</t>
+          <t>2026-10-06 23:19:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:00</t>
+          <t>2026-10-06 23:19:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:00</t>
+          <t>2026-10-06 23:19:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:30</t>
+          <t>2026-10-06 23:28:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:31</t>
+          <t>2026-10-06 23:28:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:33</t>
+          <t>2026-10-06 23:28:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:34</t>
+          <t>2026-10-06 23:28:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:34</t>
+          <t>2026-10-06 23:28:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:34</t>
+          <t>2026-10-06 23:28:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:34</t>
+          <t>2026-10-06 23:28:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:34</t>
+          <t>2026-10-06 23:28:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
